--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5284" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5284" uniqueCount="701">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -730,7 +730,7 @@
     <t>Organization.identifier.use</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>The purpose of this identifier.</t>
@@ -1406,6 +1406,9 @@
   </si>
   <si>
     <t>Organization.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -13413,16 +13416,16 @@
         <v>101</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>229</v>
+        <v>451</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -13471,7 +13474,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13486,10 +13489,10 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -13500,10 +13503,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13529,16 +13532,16 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -13587,7 +13590,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13602,13 +13605,13 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
@@ -13616,10 +13619,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13645,16 +13648,16 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>21</v>
@@ -13703,7 +13706,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13721,7 +13724,7 @@
         <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>21</v>
@@ -13732,10 +13735,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13758,19 +13761,19 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -13819,7 +13822,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13828,19 +13831,19 @@
         <v>79</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -13848,10 +13851,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13874,19 +13877,19 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -13935,7 +13938,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13944,19 +13947,19 @@
         <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
@@ -13964,10 +13967,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13993,14 +13996,14 @@
         <v>281</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14049,7 +14052,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14067,7 +14070,7 @@
         <v>388</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>105</v>
@@ -14078,10 +14081,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14104,19 +14107,19 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14165,7 +14168,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14183,7 +14186,7 @@
         <v>21</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>21</v>
@@ -14194,10 +14197,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14306,10 +14309,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14420,10 +14423,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14503,7 +14506,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14532,10 +14535,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14561,14 +14564,14 @@
         <v>239</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -14596,10 +14599,10 @@
         <v>145</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>21</v>
@@ -14617,7 +14620,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14635,7 +14638,7 @@
         <v>21</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>21</v>
@@ -14646,10 +14649,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14672,17 +14675,17 @@
         <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -14731,7 +14734,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14746,10 +14749,10 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -14760,10 +14763,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14786,17 +14789,17 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -14845,7 +14848,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14860,10 +14863,10 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>21</v>
@@ -14874,10 +14877,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14900,17 +14903,17 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -14959,7 +14962,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14974,10 +14977,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -14988,10 +14991,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15100,10 +15103,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15214,13 +15217,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="B112" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="C112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>21</v>
@@ -15242,13 +15245,13 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15328,10 +15331,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15357,16 +15360,16 @@
         <v>163</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15379,7 +15382,7 @@
         <v>21</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>21</v>
@@ -15394,10 +15397,10 @@
         <v>184</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>21</v>
@@ -15415,7 +15418,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15430,13 +15433,13 @@
         <v>99</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -15444,10 +15447,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15473,13 +15476,13 @@
         <v>163</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15493,7 +15496,7 @@
         <v>21</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>21</v>
@@ -15508,10 +15511,10 @@
         <v>184</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>21</v>
@@ -15529,7 +15532,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15544,10 +15547,10 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
@@ -15558,10 +15561,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15587,16 +15590,16 @@
         <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -15609,7 +15612,7 @@
         <v>21</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>21</v>
@@ -15645,7 +15648,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15660,10 +15663,10 @@
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>21</v>
@@ -15674,10 +15677,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15703,10 +15706,10 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15721,7 +15724,7 @@
         <v>21</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>21</v>
@@ -15757,7 +15760,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15772,13 +15775,13 @@
         <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -15786,10 +15789,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15815,10 +15818,10 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15898,10 +15901,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15927,7 +15930,7 @@
         <v>108</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>208</v>
@@ -16008,13 +16011,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>21</v>
@@ -16036,13 +16039,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16111,7 +16114,7 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -16122,10 +16125,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16234,10 +16237,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16263,7 +16266,7 @@
         <v>108</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>208</v>
@@ -16346,10 +16349,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16375,13 +16378,13 @@
         <v>129</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16389,7 +16392,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>21</v>
@@ -16431,7 +16434,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>87</v>
@@ -16460,10 +16463,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16489,10 +16492,10 @@
         <v>101</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16543,7 +16546,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16572,13 +16575,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>21</v>
@@ -16600,13 +16603,13 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16675,7 +16678,7 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>21</v>
@@ -16686,10 +16689,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16798,10 +16801,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16827,7 +16830,7 @@
         <v>108</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>208</v>
@@ -16910,10 +16913,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16939,13 +16942,13 @@
         <v>129</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16953,7 +16956,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>21</v>
@@ -16995,7 +16998,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>87</v>
@@ -17024,10 +17027,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17053,10 +17056,10 @@
         <v>101</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17107,7 +17110,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17136,13 +17139,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>21</v>
@@ -17164,13 +17167,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17239,7 +17242,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
@@ -17250,10 +17253,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17362,10 +17365,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17391,7 +17394,7 @@
         <v>108</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>208</v>
@@ -17474,10 +17477,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17503,13 +17506,13 @@
         <v>129</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17517,7 +17520,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>21</v>
@@ -17559,7 +17562,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17588,10 +17591,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17617,10 +17620,10 @@
         <v>101</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17671,7 +17674,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17700,13 +17703,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>21</v>
@@ -17728,13 +17731,13 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17794,7 +17797,7 @@
         <v>79</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>116</v>
@@ -17814,10 +17817,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17926,10 +17929,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17955,7 +17958,7 @@
         <v>108</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>208</v>
@@ -18038,10 +18041,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18067,13 +18070,13 @@
         <v>129</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18081,7 +18084,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>21</v>
@@ -18123,7 +18126,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>87</v>
@@ -18152,10 +18155,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18181,10 +18184,10 @@
         <v>101</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18235,7 +18238,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18264,10 +18267,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18293,10 +18296,10 @@
         <v>101</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18320,7 +18323,7 @@
         <v>21</v>
       </c>
       <c r="W139" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X139" t="s" s="2">
         <v>21</v>
@@ -18347,7 +18350,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18376,14 +18379,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18405,10 +18408,10 @@
         <v>101</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18423,7 +18426,7 @@
         <v>21</v>
       </c>
       <c r="T140" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U140" t="s" s="2">
         <v>21</v>
@@ -18459,7 +18462,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18474,13 +18477,13 @@
         <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
@@ -18488,14 +18491,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18517,13 +18520,13 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18537,7 +18540,7 @@
         <v>21</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>21</v>
@@ -18573,7 +18576,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18588,10 +18591,10 @@
         <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>21</v>
@@ -18602,14 +18605,14 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -18631,10 +18634,10 @@
         <v>101</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18685,7 +18688,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18700,13 +18703,13 @@
         <v>99</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -18714,14 +18717,14 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -18743,10 +18746,10 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18761,7 +18764,7 @@
         <v>21</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>21</v>
@@ -18797,7 +18800,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18812,13 +18815,13 @@
         <v>99</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -18826,10 +18829,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18855,13 +18858,13 @@
         <v>101</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18911,7 +18914,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18926,13 +18929,13 @@
         <v>99</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>21</v>
@@ -18940,10 +18943,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18969,14 +18972,14 @@
         <v>272</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -18989,7 +18992,7 @@
         <v>21</v>
       </c>
       <c r="T145" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="U145" t="s" s="2">
         <v>21</v>
@@ -19025,7 +19028,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19040,10 +19043,10 @@
         <v>99</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>278</v>
@@ -19054,10 +19057,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19080,17 +19083,17 @@
         <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -19139,7 +19142,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
